--- a/wwwroot/Data/StudentsResult.xlsx
+++ b/wwwroot/Data/StudentsResult.xlsx
@@ -3675,7 +3675,7 @@
         <v>0.10333333333333333</v>
       </c>
       <c r="AA2" s="3">
-        <f>Z2*100</f>
+        <f>Z2 *100</f>
         <v>10.333333333333334</v>
       </c>
       <c r="AB2" t="s">
@@ -3759,7 +3759,7 @@
         <v>0.61333333333333329</v>
       </c>
       <c r="AA3" s="3">
-        <f t="shared" ref="AA3:AA66" si="0">Z3*100</f>
+        <f t="shared" ref="AA3:AA66" si="0">Z3 *100</f>
         <v>61.333333333333329</v>
       </c>
       <c r="AB3" t="s">
@@ -4251,20 +4251,20 @@
         <v>538</v>
       </c>
       <c r="X9">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y9">
         <v>131</v>
       </c>
       <c r="Z9">
-        <v>0.43666666666666665</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="AA9" s="3">
         <f t="shared" si="0"/>
-        <v>43.666666666666664</v>
+        <v>65.5</v>
       </c>
       <c r="AB9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.55000000000000004">
@@ -4669,7 +4669,7 @@
         <v>69.333333333333343</v>
       </c>
       <c r="AB14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.55000000000000004">
@@ -5076,20 +5076,20 @@
         <v>538</v>
       </c>
       <c r="X19">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y19">
         <v>71</v>
       </c>
       <c r="Z19">
-        <v>0.23666666666666666</v>
+        <v>0.71</v>
       </c>
       <c r="AA19" s="3">
         <f t="shared" si="0"/>
-        <v>23.666666666666668</v>
+        <v>71</v>
       </c>
       <c r="AB19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.55000000000000004">
@@ -5244,20 +5244,20 @@
         <v>538</v>
       </c>
       <c r="X21">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y21">
         <v>127</v>
       </c>
       <c r="Z21">
-        <v>0.42333333333333334</v>
+        <v>0.63500000000000001</v>
       </c>
       <c r="AA21" s="3">
         <f t="shared" si="0"/>
-        <v>42.333333333333336</v>
+        <v>63.5</v>
       </c>
       <c r="AB21" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.55000000000000004">
@@ -9108,7 +9108,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="AA67" s="3">
-        <f t="shared" ref="AA67:AA130" si="1">Z67*100</f>
+        <f t="shared" ref="AA67:AA130" si="1">Z67 *100</f>
         <v>19.5</v>
       </c>
       <c r="AB67" t="s">
@@ -14484,7 +14484,7 @@
         <v>0.38</v>
       </c>
       <c r="AA131" s="3">
-        <f t="shared" ref="AA131:AA194" si="2">Z131*100</f>
+        <f t="shared" ref="AA131:AA194" si="2">Z131 *100</f>
         <v>38</v>
       </c>
       <c r="AB131" t="s">
@@ -19845,7 +19845,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="AA195" s="3">
-        <f t="shared" ref="AA195:AA258" si="3">Z195*100</f>
+        <f t="shared" ref="AA195:AA258" si="3">Z195 *100</f>
         <v>41.5</v>
       </c>
       <c r="AB195" t="s">
@@ -25215,7 +25215,7 @@
         <v>0.48</v>
       </c>
       <c r="AA259" s="3">
-        <f t="shared" ref="AA259:AA322" si="4">Z259*100</f>
+        <f t="shared" ref="AA259:AA322" si="4">Z259 *100</f>
         <v>48</v>
       </c>
       <c r="AB259" t="s">
@@ -30585,7 +30585,7 @@
         <v>0.4</v>
       </c>
       <c r="AA323" s="3">
-        <f t="shared" ref="AA323:AA370" si="5">Z323*100</f>
+        <f t="shared" ref="AA323:AA370" si="5">Z323 *100</f>
         <v>40</v>
       </c>
       <c r="AB323" t="s">
